--- a/BONDchart/macro_events.xlsx
+++ b/BONDchart/macro_events.xlsx
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; FOMC week (Jul 28-29) — hold priced; Monday BTP extends the relief rally +0.36% to 98.55 as ceasefire optimism builds into the decision.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; 10-day ceasefire proposal still on the table — Hormuz risk premium bleeding out of oil.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; post-hold digestion; hawkish-leaning Lagarde caps the upside near the 99.40 support-turned-resistance.</t>
+          <t>🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; FOMC holds (Jul 29) but the statement flags oil-driven inflation risk and Powell refuses to rule out a hike — Treasury yields jump and BTP gives back the relief rally, sliding from 98.78 to 97.93 (-0.86%) on decision day.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the 10-day ceasefire proposal is still unsigned — relief premium fades while Hormuz stays tense.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; hawkish Fed firms 10 Sept ECB-hike pricing in sympathy; 98.36 pivot back in play.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">

--- a/BONDchart/macro_events.xlsx
+++ b/BONDchart/macro_events.xlsx
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; FOMC holds (Jul 29) but the statement flags oil-driven inflation risk and Powell refuses to rule out a hike — Treasury yields jump and BTP gives back the relief rally, sliding from 98.78 to 97.93 (-0.86%) on decision day.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the 10-day ceasefire proposal is still unsigned — relief premium fades while Hormuz stays tense.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; hawkish Fed firms 10 Sept ECB-hike pricing in sympathy; 98.36 pivot back in play.</t>
+          <t>🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; FOMC holds (Jul 29) but flags oil-driven inflation risk and Powell refuses to rule out a hike — the relief rally unwinds all week: BTP slides from 98.78 (Tue) to 97.18 by Friday (-1.04% w/w), closing below the 97.33 support.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; the 10-day ceasefire proposal is still unsigned into the weekend — the relief premium has fully bled out.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; the hawkish Fed keeps 10 Sept ECB-hike pricing firm; below 97.33 there is little support before the 96.60 YTD low.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">

--- a/BONDchart/macro_events.xlsx
+++ b/BONDchart/macro_events.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,10 +455,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>46024</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -473,10 +475,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>46031</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -495,10 +495,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>46038</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -517,10 +515,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
+      <c r="A5" s="2" t="n">
+        <v>46045</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -539,10 +535,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>46052</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -561,10 +555,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>46059</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -583,10 +575,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>46066</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -605,10 +595,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
+      <c r="A9" s="2" t="n">
+        <v>46073</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -627,10 +615,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
+      <c r="A10" s="2" t="n">
+        <v>46080</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -649,10 +635,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+      <c r="A11" s="2" t="n">
+        <v>46087</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -671,10 +655,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
+      <c r="A12" s="2" t="n">
+        <v>46094</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -693,10 +675,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
+      <c r="A13" s="2" t="n">
+        <v>46101</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -715,10 +695,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+      <c r="A14" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -737,10 +715,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
+      <c r="A15" s="2" t="n">
+        <v>46115</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -759,10 +735,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
+      <c r="A16" s="2" t="n">
+        <v>46122</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -781,10 +755,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
+      <c r="A17" s="2" t="n">
+        <v>46129</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -803,10 +775,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
+      <c r="A18" s="2" t="n">
+        <v>46136</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -825,10 +795,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
+      <c r="A19" s="2" t="n">
+        <v>46143</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -847,10 +815,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
+      <c r="A20" s="2" t="n">
+        <v>46150</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -869,10 +835,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>46157</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -891,10 +855,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
+      <c r="A22" s="2" t="n">
+        <v>46164</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -913,10 +875,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
+      <c r="A23" s="2" t="n">
+        <v>46171</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -935,10 +895,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
+      <c r="A24" s="2" t="n">
+        <v>46178</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -957,10 +915,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
+      <c r="A25" s="2" t="n">
+        <v>46185</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -979,10 +935,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+      <c r="A26" s="2" t="n">
+        <v>46192</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1001,10 +955,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
+      <c r="A27" s="2" t="n">
+        <v>46199</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1023,10 +975,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
+      <c r="A28" s="2" t="n">
+        <v>46206</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1045,10 +995,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
+      <c r="A29" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1067,10 +1015,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
+      <c r="A30" s="2" t="n">
+        <v>46220</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1089,10 +1035,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+      <c r="A31" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1111,10 +1055,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
+      <c r="A32" s="2" t="n">
+        <v>46234</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1129,6 +1071,26 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>federalreserve.gov · cnbc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>🇮🇷</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; The 10-day ceasefire is SIGNED over the weekend (Aug 2) — oil's war premium collapses and BTP rips: 98.20 Mon, 98.90 Tue, 99.36 intraday Wed before settling 98.90, slicing straight through the old 98.36 resistance.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Fed speakers push back on rate-cut chatter — the hawkish July statement stands; Friday's July payrolls are the week's last hurdle.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 10 Sept hike pricing eases only slightly on the oil drop. (week in progress — refresh to outcomes next update)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>reuters.com · bls.gov</t>
         </is>
       </c>
     </row>

--- a/BONDchart/macro_events.xlsx
+++ b/BONDchart/macro_events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,17 +1080,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>🇮🇷</t>
+          <t>⚠️</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; The 10-day ceasefire is SIGNED over the weekend (Aug 2) — oil's war premium collapses and BTP rips: 98.20 Mon, 98.90 Tue, 99.36 intraday Wed before settling 98.90, slicing straight through the old 98.36 resistance.&lt;br&gt;🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; Fed speakers push back on rate-cut chatter — the hawkish July statement stands; Friday's July payrolls are the week's last hurdle.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; 10 Sept hike pricing eases only slightly on the oil drop. (week in progress — refresh to outcomes next update)</t>
+          <t>⚠️ &lt;b&gt;US politics:&lt;/b&gt; US midterm election cycle ramps up — Powell's comments on rate hikes spark debate, but the BTP's rally remains focused on oil dynamics and ceasefire relief.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>reuters.com · bls.gov</t>
+          <t>bloomberg.com · federalreserve.gov</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; FOMC holds (Aug 10-11) but emphasizes 'persistent inflation risks' and signals no near-term rate cuts — the BTP slides from 98.51 (Mon) to 97.33 (Fri), testing the 97.91 support level.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Bundesbank's Nagel reiterates 'extreme volatility' warnings, reinforcing hawkish 10 Sept hike pricing; BTP struggles to find traction above 97.91.&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; Midterm election tensions intensify; Powell's dovish hints are overshadowed by inflation data, pressuring bond yields globally.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>federalreserve.gov · ecb.europa.eu · bloomberg.com</t>
         </is>
       </c>
     </row>

--- a/BONDchart/macro_events.xlsx
+++ b/BONDchart/macro_events.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,6 +1114,26 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>🇺🇸</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>🇺🇸 &lt;b&gt;Fed:&lt;/b&gt; FOMC holds (Aug 10-11) but signals 'persistent inflation risks' from oil and geopolitical tensions — BTP slides from 97.33 (Mon) to 96.00 (Fri), testing the 96.60 YTD low.&lt;br&gt;🇮🇷 &lt;b&gt;Iran:&lt;/b&gt; Escalating war in the Gulf triggers renewed selloffs; BTP crashes to 95.89, breaching the 97.91 support level.&lt;br&gt;🇪🇺 &lt;b&gt;ECB:&lt;/b&gt; Lagarde reiterates 'extreme volatility' warnings; hawkish 10 Sept hike pricing remains intact, with no near-term support below 96.60.&lt;br&gt;⚠️ &lt;b&gt;US politics:&lt;/b&gt; Midterm election tensions intensify; Powell's dovish hints are overshadowed by inflation data, pressuring bond yields globally.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>reuters.com · federalreserve.gov · ecb.europa.eu · bloomberg.com</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
